--- a/quizzes/026_paint_formulation_knowledge_quiz--quizzes.xlsx
+++ b/quizzes/026_paint_formulation_knowledge_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>paint_type</t>
+          <t>paint_type_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>paint type</t>
+          <t>Paint Type 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>finish</t>
+          <t>finish (2)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>colorants</t>
+          <t>colorants (2)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'waterborne'}</t>
+          <t>waterborne</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Waterborne'}</t>
+          <t>Waterborne</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'solventborne'}</t>
+          <t>solventborne</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Solventborne'}</t>
+          <t>Solventborne</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'solventless'}</t>
+          <t>solventless</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Solventless'}</t>
+          <t>Solventless</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'high-pressure'}</t>
+          <t>high-pressure</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'High-Pressure'}</t>
+          <t>High-Pressure</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'powder'}</t>
+          <t>powder</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Powder'}</t>
+          <t>Powder</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'powder_coating'}</t>
+          <t>powder_coating</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Powder Coating'}</t>
+          <t>Powder Coating</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'resin'}</t>
+          <t>resin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Resin'}</t>
+          <t>Resin</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'latex'}</t>
+          <t>latex</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Latex'}</t>
+          <t>Latex</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'alkyd'}</t>
+          <t>alkyd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Alkyd'}</t>
+          <t>Alkyd</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'epoxy'}</t>
+          <t>epoxy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Epoxy'}</t>
+          <t>Epoxy</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'acrylic'}</t>
+          <t>acrylic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Acrylic'}</t>
+          <t>Acrylic</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'polyester'}</t>
+          <t>polyester</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Polyester'}</t>
+          <t>Polyester</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'urethane'}</t>
+          <t>urethane</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Urethane'}</t>
+          <t>Urethane</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'urethane/alkyd'}</t>
+          <t>urethane/alkyd</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Urethane/Alkyd'}</t>
+          <t>Urethane/Alkyd</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'polyurethane'}</t>
+          <t>polyurethane</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Polyurethane'}</t>
+          <t>Polyurethane</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'solvent'}</t>
+          <t>solvent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Solvent'}</t>
+          <t>Solvent</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'water'}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Water'}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'organic'}</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Organic'}</t>
+          <t>Organic</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'silica'}</t>
+          <t>silica</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Silica'}</t>
+          <t>Silica</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'calcium_carbonate'}</t>
+          <t>calcium_carbonate</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Calcium Carbonate'}</t>
+          <t>Calcium Carbonate</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'talc'}</t>
+          <t>talc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Talc'}</t>
+          <t>Talc</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'silica/silica'}</t>
+          <t>silica/silica</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Silica/Silica'}</t>
+          <t>Silica/Silica</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pigments'}</t>
+          <t>pigments</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pigments'}</t>
+          <t>Pigments</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dyes'}</t>
+          <t>dyes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Dyes'}</t>
+          <t>Dyes</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'interlayers'}</t>
+          <t>interlayers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Interlayers'}</t>
+          <t>Interlayers</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'pint'}</t>
+          <t>pint</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Pint'}</t>
+          <t>Pint</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'matte'}</t>
+          <t>matte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Matte'}</t>
+          <t>Matte</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'gloss'}</t>
+          <t>gloss</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Gloss'}</t>
+          <t>Gloss</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'semi_gloss'}</t>
+          <t>semi_gloss</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Semi Gloss'}</t>
+          <t>Semi Gloss</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'titanium_dioxide'}</t>
+          <t>titanium_dioxide</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Titanium Dioxide'}</t>
+          <t>Titanium Dioxide</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'iron_oxide'}</t>
+          <t>iron_oxide</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Iron Oxide'}</t>
+          <t>Iron Oxide</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'carbon_black'}</t>
+          <t>carbon_black</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Carbon Black'}</t>
+          <t>Carbon Black</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'matt'}</t>
+          <t>matt</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Matt'}</t>
+          <t>Matt</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'semi-gloss'}</t>
+          <t>semi-gloss</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Semi-gloss'}</t>
+          <t>Semi-gloss</t>
         </is>
       </c>
     </row>
@@ -1828,97 +1828,97 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'high-gloss'}</t>
+          <t>high-gloss</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'High-Gloss'}</t>
+          <t>High-Gloss</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>paint_type_choices</t>
+          <t>paint_type_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'waterborne'}</t>
+          <t>waterborne</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Waterborne'}</t>
+          <t>Waterborne</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>paint_type_choices</t>
+          <t>paint_type_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'solventborne'}</t>
+          <t>solventborne</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Solventborne'}</t>
+          <t>Solventborne</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>paint_type_choices</t>
+          <t>paint_type_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'solventless'}</t>
+          <t>solventless</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Solventless'}</t>
+          <t>Solventless</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>paint_type_choices</t>
+          <t>paint_type_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'high-pressure'}</t>
+          <t>high-pressure</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'High-Pressure'}</t>
+          <t>High-Pressure</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>paint_type_choices</t>
+          <t>paint_type_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'powder'}</t>
+          <t>powder</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Powder'}</t>
+          <t>Powder</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'matte'}</t>
+          <t>matte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Matte'}</t>
+          <t>Matte</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'gloss'}</t>
+          <t>gloss</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Gloss'}</t>
+          <t>Gloss</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'semi-gloss'}</t>
+          <t>semi-gloss</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Semi-gloss'}</t>
+          <t>Semi-gloss</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pigments'}</t>
+          <t>pigments</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pigments'}</t>
+          <t>Pigments</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dyes'}</t>
+          <t>dyes</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Dyes'}</t>
+          <t>Dyes</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'interlayers'}</t>
+          <t>interlayers</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Interlayers'}</t>
+          <t>Interlayers</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
